--- a/output/【PO2603230466】IV&PL.xlsx
+++ b/output/【PO2603230466】IV&PL.xlsx
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="11" t="n">
-        <v>3918909000</v>
+        <v>3918909001</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3918909000</v>
+        <v>3918909001</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>10.15505009873474</v>
+        <v>9.308795923840172</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="n">
-        <v>3918909000</v>
+        <v>3918909001</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>22.45020112630732</v>
+        <v>20.40927375118847</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="11" t="n">
-        <v>3918909000</v>
+        <v>3918909001</v>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>18.70850093858943</v>
+        <v>22.45020112630732</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="11" t="n">
-        <v>3918909000</v>
+        <v>3918909001</v>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="D15" s="14" t="n">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="11" t="n">
-        <v>3918909000</v>
+        <v>3918909001</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3918909000</v>
+        <v>3918909001</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -1247,16 +1247,16 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>211.2</v>
+        <v>230.4</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>1.49737</v>
+        <v>1.6335</v>
       </c>
     </row>
     <row r="11" ht="70" customHeight="1">
@@ -1264,7 +1264,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="n">
-        <v>3918909000</v>
+        <v>3918909001</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>228</v>
+        <v>250.8</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>1.0449</v>
+        <v>1.14939</v>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
@@ -1297,7 +1297,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="11" t="n">
-        <v>3918909000</v>
+        <v>3918909001</v>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>136.8</v>
+        <v>114</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>0.6269400000000001</v>
+        <v>0.52245</v>
       </c>
     </row>
     <row r="13" ht="74" customHeight="1">
@@ -1330,7 +1330,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="11" t="n">
-        <v>3918909000</v>
+        <v>3918909001</v>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="D15" s="14" t="n">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
@@ -1378,16 +1378,16 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>742.2</v>
+        <v>761.4</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>920.8</v>
+        <v>944.8</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>4.77167</v>
+        <v>4.90779</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1"/>
